--- a/diseases/d088/2010-2014.xlsx
+++ b/diseases/d088/2010-2014.xlsx
@@ -8805,6 +8805,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
@@ -8822,7 +8827,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -8833,6 +8843,11 @@
       <c r="AT59" t="n">
         <v>1</v>
       </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -8855,22 +8870,22 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -8897,17 +8912,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8948,7 +8963,32 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8956,6 +8996,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN60" t="b">
+        <v>1</v>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -8963,55 +9061,65 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
         <v>1</v>
       </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9043,12 +9151,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9184,12 +9292,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9325,12 +9433,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9466,12 +9574,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9607,12 +9715,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9748,12 +9856,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9889,12 +9997,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10030,12 +10138,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10069,10 +10177,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10171,12 +10279,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10210,10 +10318,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10312,12 +10420,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10453,12 +10561,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10594,12 +10702,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10735,12 +10843,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10876,12 +10984,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11017,12 +11125,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11158,12 +11266,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11299,12 +11407,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11440,12 +11548,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11581,12 +11689,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11611,12 +11719,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -11625,12 +11733,9 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11650,7 +11755,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -11658,42 +11763,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11725,12 +11830,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11769,9 +11874,17 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11786,55 +11899,65 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
         <v>1</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11861,17 +11984,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11912,7 +12035,32 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11920,6 +12068,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -11927,55 +12133,65 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
         <v>1</v>
       </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12007,12 +12223,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12148,12 +12364,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12289,12 +12505,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12430,12 +12646,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12571,12 +12787,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12712,12 +12928,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12853,12 +13069,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -12994,12 +13210,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13135,12 +13351,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13276,12 +13492,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13417,12 +13633,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13558,12 +13774,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13699,12 +13915,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13840,12 +14056,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13981,12 +14197,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14122,12 +14338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14161,10 +14377,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -14263,12 +14479,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14371,6 +14587,288 @@
         </is>
       </c>
       <c r="BC98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NZ-WKO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Waikato, New Zealand</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NZ-WMT</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Waitemata, New Zealand</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14502,7 +15000,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -14522,7 +15020,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -14532,7 +15030,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
